--- a/utils/monday_sprint_sprint_2024-46.xlsx
+++ b/utils/monday_sprint_sprint_2024-46.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="151">
   <si>
     <t>Ticket</t>
   </si>
@@ -87,7 +87,7 @@
     <t>09/09/2024</t>
   </si>
   <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -3288,7 +3288,7 @@
         <v>26</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3311,10 +3311,10 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
@@ -3331,13 +3331,13 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Q13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
         <v>145</v>
       </c>
@@ -3348,12 +3348,6 @@
         <v>25</v>
       </c>
       <c r="N14">
-        <v>5</v>
-      </c>
-      <c r="P14" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q14">
         <v>5</v>
       </c>
     </row>
@@ -3408,7 +3402,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>18</v>

--- a/utils/monday_sprint_sprint_2024-46.xlsx
+++ b/utils/monday_sprint_sprint_2024-46.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="188">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -105,7 +105,7 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>7539198948</t>
   </si>
   <si>
     <t>Categoria não informada</t>
@@ -123,22 +123,19 @@
     <t>01/10/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>02/10/2024</t>
   </si>
   <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Outubro</t>
   </si>
   <si>
-    <t>28241</t>
+    <t>7521664624</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -150,10 +147,13 @@
     <t>27/09/2024</t>
   </si>
   <si>
+    <t>12/10/2024</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>7529180746</t>
   </si>
   <si>
     <t>Interface de visualização de conjuntos</t>
@@ -165,13 +165,19 @@
     <t>30/09/2024</t>
   </si>
   <si>
+    <t>03/10/2024</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
+    <t>7529180776</t>
+  </si>
+  <si>
     <t>Nova Visualização para Modelos Conjunto na Tela de Vinculação de Sequencias</t>
   </si>
   <si>
-    <t>28037</t>
+    <t>7578395166</t>
   </si>
   <si>
     <t>Login de Admin</t>
@@ -180,7 +186,10 @@
     <t>07/10/2024</t>
   </si>
   <si>
-    <t>28086</t>
+    <t>10/10/2024</t>
+  </si>
+  <si>
+    <t>7520993422</t>
   </si>
   <si>
     <t>Tempos de Ajustagem</t>
@@ -189,31 +198,31 @@
     <t>Feito</t>
   </si>
   <si>
-    <t>28120</t>
+    <t>7520173875</t>
   </si>
   <si>
     <t>Melhoria no calculo DIFAL</t>
   </si>
   <si>
-    <t>28083</t>
+    <t>7520233253</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Revisão Contas Contábeis - Crédito de Impostos</t>
   </si>
   <si>
-    <t>27997</t>
+    <t>7521334142</t>
   </si>
   <si>
     <t>Inclusão de coluna - Planilha produtivo</t>
   </si>
   <si>
-    <t>28044</t>
+    <t>7521084103</t>
   </si>
   <si>
     <t>Incluir Motivo de parada - Rebarbações VI e VII</t>
   </si>
   <si>
-    <t>27886</t>
+    <t>7428486831</t>
   </si>
   <si>
     <t>Registro de inspeção</t>
@@ -222,52 +231,67 @@
     <t>A fazer</t>
   </si>
   <si>
-    <t>28025</t>
+    <t>7521276983</t>
   </si>
   <si>
     <t>Síntese de reunião - Projeto IROG - Matriz</t>
   </si>
   <si>
-    <t>28121</t>
+    <t>7520830916</t>
   </si>
   <si>
     <t>[NIMBI] Criação da rotina que integra os pedidos a cada 30 min</t>
   </si>
   <si>
-    <t>28104</t>
+    <t>28/11/2024</t>
+  </si>
+  <si>
+    <t>7520874698</t>
   </si>
   <si>
     <t>CONTAS A PAGAR BENNER: DADOS BANCARIOS / ALERTAS ADTO REMESSA</t>
   </si>
   <si>
+    <t>7539144432</t>
+  </si>
+  <si>
     <t>Sistema para Faseamento de Vendas e Faturamento / Obter a KB</t>
   </si>
   <si>
+    <t>7539178265</t>
+  </si>
+  <si>
     <t>Sistema para Faseamento de Vendas e Faturamento / Estrutura de dados</t>
   </si>
   <si>
+    <t>7539188811</t>
+  </si>
+  <si>
     <t>Sistema para Faseamento de Vendas e Faturamento / Importar planilha.</t>
   </si>
   <si>
+    <t>7539195691</t>
+  </si>
+  <si>
     <t>Sistema para Faseamento de Vendas e Faturamento / Exportar planilha</t>
   </si>
   <si>
-    <t>28207</t>
+    <t>08/10/2024</t>
+  </si>
+  <si>
+    <t>7549996871</t>
   </si>
   <si>
     <t>Relatório que extraia do sistema as notas de entradas que foram lançadas com o CFOP</t>
   </si>
   <si>
-    <t>02/10/2024</t>
+    <t>7558574071</t>
   </si>
   <si>
     <t>Fazer rateio do tempo padrão ao finalizar apontamento da inspeção</t>
   </si>
   <si>
-    <t>03/10/2024</t>
-  </si>
-  <si>
-    <t>27532</t>
+    <t>7327706448</t>
   </si>
   <si>
     <t>Planilha Carga Máquina</t>
@@ -282,33 +306,39 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>28013</t>
+    <t>7520305733</t>
   </si>
   <si>
     <t>Melhoria sistema de embalagem</t>
   </si>
   <si>
-    <t>27982</t>
+    <t>7520338128</t>
   </si>
   <si>
     <t>Sistema de informação de notas recebidas - Empresas do grupo</t>
   </si>
   <si>
-    <t>28117</t>
+    <t>7520213001</t>
   </si>
   <si>
     <t>Melhoria continua lançamento NFs</t>
   </si>
   <si>
-    <t>27942</t>
+    <t>7520403674</t>
   </si>
   <si>
     <t>Sistema de Invoice - Invoice for payment (CRITICO)</t>
   </si>
   <si>
+    <t>06/10/2024</t>
+  </si>
+  <si>
     <t>27915</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>Komatsu - SUGESTÃO OPÇÕES DE APONTAMENTO - RETIRAR 1 OPERAÇÃO, ADICIONAR 04 OPERAÇÕES!</t>
   </si>
   <si>
@@ -318,13 +348,13 @@
     <t>Enzo Luiz Okabe Auad</t>
   </si>
   <si>
-    <t>28073</t>
+    <t>7520253743</t>
   </si>
   <si>
     <t>FORMULARIOS SETOR 549</t>
   </si>
   <si>
-    <t>26896</t>
+    <t>7529851704</t>
   </si>
   <si>
     <t>Correção</t>
@@ -333,49 +363,55 @@
     <t>Margem de Contribuição nas Ofertas -  verificar chamado</t>
   </si>
   <si>
-    <t>27892</t>
+    <t>7529775836</t>
   </si>
   <si>
     <t>Janelas de Pagamento - Alteração Integração Benner</t>
   </si>
   <si>
-    <t>27913</t>
+    <t>7520615305</t>
   </si>
   <si>
     <t>Bloqueio importação de CT-e</t>
   </si>
   <si>
-    <t>27820</t>
+    <t>7520661939</t>
   </si>
   <si>
     <t>PARADAS APONTAMENTOS ELETRONICOS E APONTMAENTO TABLET</t>
   </si>
   <si>
-    <t>27863</t>
+    <t>7520633148</t>
   </si>
   <si>
     <t>Alerta de Procedimento Pré-Produtivo - Impressão</t>
   </si>
   <si>
-    <t>28127</t>
+    <t>13/10/2024</t>
+  </si>
+  <si>
+    <t>7520813331</t>
   </si>
   <si>
     <t>Alteração de Regra - Grupo de Ligas</t>
   </si>
   <si>
-    <t>28065</t>
+    <t>7521044361</t>
   </si>
   <si>
     <t>Peças UPR &gt; Avaliação Ronda</t>
   </si>
   <si>
-    <t>28101</t>
+    <t>11/10/2024</t>
+  </si>
+  <si>
+    <t>7520939902</t>
   </si>
   <si>
     <t>ALTERAÇÃO FILTRO GESTÃO A VISTA</t>
   </si>
   <si>
-    <t>27960</t>
+    <t>7454578342</t>
   </si>
   <si>
     <t>Plataforma de Indicadores - Alterações - Chamado Matriz</t>
@@ -384,61 +420,76 @@
     <t>18/09/2024</t>
   </si>
   <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
+    <t>7539332173</t>
+  </si>
+  <si>
     <t>Não atrelar os indicadores ao centro custo, se possível retirar os centros de custo e mudar para “setores”</t>
   </si>
   <si>
+    <t>7539347061</t>
+  </si>
+  <si>
     <t>Quando eu insiro os resultados de cada mês, em manutenção do indicador</t>
   </si>
   <si>
+    <t>7539352635</t>
+  </si>
+  <si>
     <t>O cadastro está acontecendo em 3 etapas</t>
   </si>
   <si>
+    <t>7539381652</t>
+  </si>
+  <si>
     <t>Quando eu seleciono “valor abaixo ok” no cadastro</t>
   </si>
   <si>
-    <t>28168</t>
+    <t>7550130425</t>
   </si>
   <si>
     <t>Programação moldagem - trava de CPP bloqueados</t>
   </si>
   <si>
-    <t>27691</t>
+    <t>7558829971</t>
   </si>
   <si>
     <t>Melhoria Sistema - Materiais Indiretos - MADEIRA PARA MODELOS</t>
   </si>
   <si>
+    <t>7570637369</t>
+  </si>
+  <si>
     <t>NF vencida, considerar a data atual +10 dias e aplicar calculo da janela de vencimento</t>
   </si>
   <si>
     <t>04/10/2024</t>
   </si>
   <si>
-    <t>28279</t>
+    <t>7616201538</t>
   </si>
   <si>
     <t>Lançar sequências 924IK/925IK/926IK/927IK/928IK/929IK</t>
   </si>
   <si>
-    <t>11/10/2024</t>
-  </si>
-  <si>
-    <t>28052</t>
+    <t>7521055353</t>
   </si>
   <si>
     <t>Auditoria de saúde e segurança ocupacional - Digital</t>
   </si>
   <si>
-    <t>28040</t>
+    <t>7521114238</t>
   </si>
   <si>
     <t>Auditoria de saúde e segurança ocupacional</t>
   </si>
   <si>
-    <t>28134</t>
+    <t>7522239371</t>
   </si>
   <si>
     <t>Bloqueio programação de moldagem</t>
@@ -453,7 +504,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-46</t>
+    <t>Ago/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1092,48 +1143,48 @@
         <v>37</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>26</v>
@@ -1180,7 +1231,7 @@
         <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>26</v>
@@ -1189,7 +1240,7 @@
         <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>29</v>
@@ -1197,7 +1248,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1209,10 +1260,10 @@
         <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
@@ -1227,7 +1278,7 @@
         <v>49</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>26</v>
@@ -1236,7 +1287,7 @@
         <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>29</v>
@@ -1244,7 +1295,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1256,10 +1307,10 @@
         <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
@@ -1271,10 +1322,10 @@
         <v>34</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>26</v>
@@ -1283,15 +1334,15 @@
         <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1303,10 +1354,10 @@
         <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
@@ -1318,13 +1369,13 @@
         <v>34</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>27</v>
@@ -1338,7 +1389,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1350,10 +1401,10 @@
         <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
@@ -1365,13 +1416,13 @@
         <v>34</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>27</v>
@@ -1385,40 +1436,40 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>27</v>
@@ -1432,7 +1483,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1444,10 +1495,10 @@
         <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
@@ -1459,13 +1510,13 @@
         <v>34</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>27</v>
@@ -1479,7 +1530,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1491,10 +1542,10 @@
         <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
@@ -1506,13 +1557,13 @@
         <v>34</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>27</v>
@@ -1526,7 +1577,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1538,10 +1589,10 @@
         <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>21</v>
@@ -1556,13 +1607,13 @@
         <v>24</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>28</v>
@@ -1573,7 +1624,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1585,10 +1636,10 @@
         <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
@@ -1600,16 +1651,16 @@
         <v>34</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>45</v>
@@ -1620,7 +1671,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1632,10 +1683,10 @@
         <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
@@ -1647,13 +1698,13 @@
         <v>34</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>27</v>
@@ -1667,7 +1718,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1679,10 +1730,10 @@
         <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
@@ -1694,13 +1745,13 @@
         <v>34</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>27</v>
@@ -1714,7 +1765,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1726,10 +1777,10 @@
         <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
@@ -1744,24 +1795,24 @@
         <v>35</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O17" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1773,10 +1824,10 @@
         <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
@@ -1791,24 +1842,24 @@
         <v>35</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O18" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1820,10 +1871,10 @@
         <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
@@ -1838,24 +1889,24 @@
         <v>35</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O19" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1867,10 +1918,10 @@
         <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
@@ -1885,24 +1936,24 @@
         <v>35</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1914,10 +1965,10 @@
         <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
@@ -1929,27 +1980,27 @@
         <v>34</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1961,10 +2012,10 @@
         <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
@@ -1976,27 +2027,27 @@
         <v>34</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2008,13 +2059,13 @@
         <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>33</v>
@@ -2023,27 +2074,27 @@
         <v>34</v>
       </c>
       <c r="J23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="L23" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2055,10 +2106,10 @@
         <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
@@ -2070,13 +2121,13 @@
         <v>34</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>27</v>
@@ -2090,7 +2141,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2102,10 +2153,10 @@
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
@@ -2117,13 +2168,13 @@
         <v>34</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>27</v>
@@ -2137,7 +2188,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2149,10 +2200,10 @@
         <v>31</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
@@ -2164,13 +2215,13 @@
         <v>34</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>27</v>
@@ -2184,7 +2235,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2196,10 +2247,10 @@
         <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>48</v>
@@ -2211,13 +2262,13 @@
         <v>34</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>27</v>
@@ -2231,10 +2282,10 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
@@ -2243,28 +2294,28 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>27</v>
@@ -2278,7 +2329,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2290,10 +2341,10 @@
         <v>31</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
@@ -2305,13 +2356,13 @@
         <v>34</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>27</v>
@@ -2325,22 +2376,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>21</v>
@@ -2355,16 +2406,16 @@
         <v>49</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>29</v>
@@ -2372,7 +2423,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2384,10 +2435,10 @@
         <v>31</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>48</v>
@@ -2402,16 +2453,16 @@
         <v>49</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>29</v>
@@ -2419,7 +2470,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2431,10 +2482,10 @@
         <v>31</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>21</v>
@@ -2446,13 +2497,13 @@
         <v>34</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>27</v>
@@ -2466,7 +2517,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2478,10 +2529,10 @@
         <v>31</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>21</v>
@@ -2493,13 +2544,13 @@
         <v>34</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>27</v>
@@ -2513,7 +2564,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2525,10 +2576,10 @@
         <v>31</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>21</v>
@@ -2540,13 +2591,13 @@
         <v>34</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>27</v>
@@ -2560,7 +2611,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2572,10 +2623,10 @@
         <v>31</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>21</v>
@@ -2587,13 +2638,13 @@
         <v>34</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>27</v>
@@ -2607,7 +2658,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2619,10 +2670,10 @@
         <v>31</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
@@ -2634,13 +2685,13 @@
         <v>34</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>27</v>
@@ -2654,7 +2705,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2666,10 +2717,10 @@
         <v>31</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>21</v>
@@ -2681,13 +2732,13 @@
         <v>34</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>27</v>
@@ -2701,7 +2752,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2713,10 +2764,10 @@
         <v>31</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
@@ -2728,19 +2779,19 @@
         <v>34</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>29</v>
@@ -2748,7 +2799,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2760,10 +2811,10 @@
         <v>31</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>21</v>
@@ -2778,24 +2829,24 @@
         <v>35</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O39" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2807,10 +2858,10 @@
         <v>31</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
@@ -2825,24 +2876,24 @@
         <v>35</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O40" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2854,10 +2905,10 @@
         <v>31</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>21</v>
@@ -2872,24 +2923,24 @@
         <v>35</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O41" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2901,10 +2952,10 @@
         <v>31</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>21</v>
@@ -2919,24 +2970,24 @@
         <v>35</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O42" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2948,42 +2999,42 @@
         <v>31</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K43" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="L43" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N43" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O43" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -2995,10 +3046,10 @@
         <v>31</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>21</v>
@@ -3010,27 +3061,27 @@
         <v>34</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O44" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3042,10 +3093,10 @@
         <v>31</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>48</v>
@@ -3057,42 +3108,42 @@
         <v>34</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O45" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>21</v>
@@ -3104,13 +3155,13 @@
         <v>34</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>27</v>
@@ -3119,12 +3170,12 @@
         <v>28</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3136,10 +3187,10 @@
         <v>31</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>21</v>
@@ -3151,16 +3202,16 @@
         <v>34</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>45</v>
@@ -3171,22 +3222,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>21</v>
@@ -3198,16 +3249,16 @@
         <v>34</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>45</v>
@@ -3218,7 +3269,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3230,10 +3281,10 @@
         <v>31</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>21</v>
@@ -3245,16 +3296,16 @@
         <v>34</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>45</v>
@@ -3276,23 +3327,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3300,16 +3351,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3320,20 +3371,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>574</v>
+        <v>23.05</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K22">
         <v>35</v>
@@ -3349,7 +3400,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3380,12 +3431,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B2">
         <v>48</v>
@@ -3399,35 +3450,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>574</v>
+        <v>23.05</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3435,7 +3486,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -3444,33 +3495,39 @@
         <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N10">
         <v>35</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3485,10 +3542,10 @@
         <v>27</v>
       </c>
       <c r="K11">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -3497,12 +3554,12 @@
         <v>28</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3514,13 +3571,13 @@
         <v>43</v>
       </c>
       <c r="J12" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -3529,12 +3586,12 @@
         <v>45</v>
       </c>
       <c r="Q12">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -3546,15 +3603,15 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q13">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -3568,7 +3625,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3576,7 +3633,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3584,7 +3641,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3592,10 +3649,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3603,7 +3660,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3611,142 +3668,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>559</v>
+        <v>643</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>61</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
